--- a/literature-review/initial-search/initial_search_topic2.xlsx
+++ b/literature-review/initial-search/initial_search_topic2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="1" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="1" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\177020724\Documents\Studium\Thesis\Literature Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8430CF2E-4079-43F0-81FA-D17594E974DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7DA24F-C4FB-4615-BA28-177150A46D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12732" yWindow="1272" windowWidth="26556" windowHeight="14472" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4488" yWindow="936" windowWidth="30960" windowHeight="14244" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="128">
   <si>
     <t>Pretrain Vision and Large Language Models in Python: End-to-end techniques for building and deploying foundation models on AWS</t>
   </si>
@@ -401,6 +401,9 @@
   </si>
   <si>
     <t>3 Most relevant papers that have been added to the snowballing base set</t>
+  </si>
+  <si>
+    <t>Technical MLOps solution is only described in a few bullet points</t>
   </si>
 </sst>
 </file>
@@ -424,7 +427,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -440,6 +443,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D79B"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -496,7 +505,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -519,19 +528,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="fill"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -547,12 +543,31 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="fill"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFC4D79B"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1032,79 +1047,81 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="11"/>
     </row>
-    <row r="6" spans="1:17" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <v>3</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="6">
         <v>2024</v>
       </c>
-      <c r="E6" s="20">
+      <c r="E6" s="6">
         <v>0</v>
       </c>
-      <c r="F6" s="18" t="s">
+      <c r="F6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="18" t="s">
+      <c r="G6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="H6" s="19" t="s">
+      <c r="H6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="21"/>
-      <c r="J6" s="20" t="s">
+      <c r="I6" s="8"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="11"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <v>4</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="6">
+        <v>2023</v>
+      </c>
+      <c r="E7" s="6">
+        <v>0</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I7" s="8"/>
+      <c r="J7" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="K6" s="20"/>
-      <c r="L6" s="21"/>
-      <c r="M6" s="20"/>
-      <c r="N6" s="20"/>
-      <c r="O6" s="20"/>
-      <c r="P6" s="20"/>
-      <c r="Q6" s="22"/>
-    </row>
-    <row r="7" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
-        <v>4</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="D7" s="14">
-        <v>2023</v>
-      </c>
-      <c r="E7" s="14">
-        <v>0</v>
-      </c>
-      <c r="F7" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I7" s="15"/>
-      <c r="J7" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="K7" s="14"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="16"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q7" s="11" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
@@ -1283,42 +1300,42 @@
       <c r="P12" s="6"/>
       <c r="Q12" s="11"/>
     </row>
-    <row r="13" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="12">
+    <row r="13" spans="1:17" s="24" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="19">
         <v>10</v>
       </c>
-      <c r="B13" s="12" t="s">
+      <c r="B13" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="21">
         <v>2024</v>
       </c>
-      <c r="E13" s="14">
+      <c r="E13" s="21">
         <v>6</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="G13" s="12" t="s">
+      <c r="G13" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="H13" s="13" t="s">
+      <c r="H13" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="I13" s="15"/>
-      <c r="J13" s="14" t="s">
+      <c r="I13" s="22"/>
+      <c r="J13" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="K13" s="14"/>
-      <c r="L13" s="15"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
-      <c r="Q13" s="16"/>
+      <c r="K13" s="21"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="21"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="23"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
@@ -1355,42 +1372,42 @@
       <c r="P14" s="6"/>
       <c r="Q14" s="11"/>
     </row>
-    <row r="15" spans="1:17" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="18">
+    <row r="15" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="13">
         <v>12</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D15" s="20">
+      <c r="D15" s="15">
         <v>2023</v>
       </c>
-      <c r="E15" s="20">
+      <c r="E15" s="15">
         <v>12</v>
       </c>
-      <c r="F15" s="18" t="s">
+      <c r="F15" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G15" s="18" t="s">
+      <c r="G15" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="H15" s="19" t="s">
+      <c r="H15" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="I15" s="21"/>
-      <c r="J15" s="20" t="s">
+      <c r="I15" s="16"/>
+      <c r="J15" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="K15" s="20"/>
-      <c r="L15" s="21"/>
-      <c r="M15" s="20"/>
-      <c r="N15" s="20"/>
-      <c r="O15" s="20"/>
-      <c r="P15" s="20"/>
-      <c r="Q15" s="22"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="16"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="15"/>
+      <c r="P15" s="15"/>
+      <c r="Q15" s="17"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
@@ -1402,7 +1419,9 @@
       <c r="C16" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="6"/>
+      <c r="D16" s="6">
+        <v>2019</v>
+      </c>
       <c r="E16" s="6">
         <v>0</v>
       </c>
@@ -1420,7 +1439,9 @@
       <c r="K16" s="6"/>
       <c r="L16" s="8"/>
       <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
+      <c r="N16" s="6" t="s">
+        <v>121</v>
+      </c>
       <c r="O16" s="6"/>
       <c r="P16" s="6"/>
       <c r="Q16" s="11"/>
@@ -1569,42 +1590,42 @@
       <c r="P20" s="6"/>
       <c r="Q20" s="11"/>
     </row>
-    <row r="21" spans="1:17" s="23" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="18">
+    <row r="21" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="13">
         <v>18</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="D21" s="20">
+      <c r="D21" s="15">
         <v>2023</v>
       </c>
-      <c r="E21" s="20">
+      <c r="E21" s="15">
         <v>0</v>
       </c>
-      <c r="F21" s="18" t="s">
+      <c r="F21" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="G21" s="18" t="s">
+      <c r="G21" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="H21" s="19" t="s">
+      <c r="H21" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="I21" s="21"/>
-      <c r="J21" s="20" t="s">
+      <c r="I21" s="16"/>
+      <c r="J21" s="15" t="s">
         <v>122</v>
       </c>
-      <c r="K21" s="20"/>
-      <c r="L21" s="21"/>
-      <c r="M21" s="20"/>
-      <c r="N21" s="20"/>
-      <c r="O21" s="20"/>
-      <c r="P21" s="20"/>
-      <c r="Q21" s="22"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="16"/>
+      <c r="M21" s="15"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="15"/>
+      <c r="P21" s="15"/>
+      <c r="Q21" s="17"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
@@ -1686,7 +1707,9 @@
       <c r="C24" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D24" s="6"/>
+      <c r="D24" s="6">
+        <v>2024</v>
+      </c>
       <c r="E24" s="6">
         <v>0</v>
       </c>
@@ -1719,7 +1742,9 @@
       <c r="C25" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="D25" s="6"/>
+      <c r="D25" s="6">
+        <v>2024</v>
+      </c>
       <c r="E25" s="6">
         <v>1</v>
       </c>
@@ -1883,12 +1908,12 @@
       <c r="Q29" s="11"/>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B31" s="17" t="s">
+      <c r="B31" s="12" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B32" s="23" t="s">
+      <c r="B32" s="18" t="s">
         <v>126</v>
       </c>
     </row>

--- a/literature-review/initial-search/initial_search_topic2.xlsx
+++ b/literature-review/initial-search/initial_search_topic2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\177020724\Documents\Studium\Thesis\Literature Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8430CF2E-4079-43F0-81FA-D17594E974DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A18EAE81-3D37-4888-97B9-D8CF44022BAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12732" yWindow="1272" windowWidth="26556" windowHeight="14472" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6696" yWindow="-17388" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="128">
   <si>
     <t>Pretrain Vision and Large Language Models in Python: End-to-end techniques for building and deploying foundation models on AWS</t>
   </si>
@@ -401,6 +401,9 @@
   </si>
   <si>
     <t>3 Most relevant papers that have been added to the snowballing base set</t>
+  </si>
+  <si>
+    <t>Technical MLOps solution is only described in a few bullet points</t>
   </si>
 </sst>
 </file>
@@ -852,16 +855,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="31.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="31.1015625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="5.77734375" customWidth="1"/>
-    <col min="2" max="2" width="60.77734375" customWidth="1"/>
-    <col min="3" max="3" width="30.77734375" customWidth="1"/>
-    <col min="4" max="8" width="10.77734375" customWidth="1"/>
-    <col min="9" max="16" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="5.7890625" customWidth="1"/>
+    <col min="2" max="2" width="60.7890625" customWidth="1"/>
+    <col min="3" max="3" width="30.7890625" customWidth="1"/>
+    <col min="4" max="8" width="10.7890625" customWidth="1"/>
+    <col min="9" max="16" width="8.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="I1" s="2" t="s">
         <v>111</v>
       </c>
@@ -872,7 +875,7 @@
       </c>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
         <v>103</v>
       </c>
@@ -925,7 +928,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="5">
         <v>0</v>
       </c>
@@ -962,7 +965,7 @@
       <c r="P3" s="6"/>
       <c r="Q3" s="11"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -997,7 +1000,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="11"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5">
         <v>2</v>
       </c>
@@ -1032,7 +1035,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="11"/>
     </row>
-    <row r="6" spans="1:17" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" s="23" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="18">
         <v>3</v>
       </c>
@@ -1069,44 +1072,48 @@
       <c r="P6" s="20"/>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" s="5">
         <v>4</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="6">
         <v>2023</v>
       </c>
-      <c r="E7" s="14">
+      <c r="E7" s="6">
         <v>0</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="12" t="s">
+      <c r="G7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I7" s="15"/>
-      <c r="J7" s="14" t="s">
+      <c r="I7" s="8"/>
+      <c r="J7" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="K7" s="14"/>
-      <c r="L7" s="15"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
-      <c r="Q7" s="16"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="K7" s="6"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q7" s="11" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5">
         <v>5</v>
       </c>
@@ -1141,7 +1148,7 @@
       <c r="P8" s="6"/>
       <c r="Q8" s="11"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="5">
         <v>6</v>
       </c>
@@ -1176,7 +1183,7 @@
       <c r="P9" s="6"/>
       <c r="Q9" s="11"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5">
         <v>7</v>
       </c>
@@ -1211,7 +1218,7 @@
       <c r="P10" s="6"/>
       <c r="Q10" s="11"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="5">
         <v>8</v>
       </c>
@@ -1246,7 +1253,7 @@
       <c r="P11" s="6"/>
       <c r="Q11" s="11"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5">
         <v>9</v>
       </c>
@@ -1283,7 +1290,7 @@
       <c r="P12" s="6"/>
       <c r="Q12" s="11"/>
     </row>
-    <row r="13" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="12">
         <v>10</v>
       </c>
@@ -1320,7 +1327,7 @@
       <c r="P13" s="14"/>
       <c r="Q13" s="16"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5">
         <v>11</v>
       </c>
@@ -1355,7 +1362,7 @@
       <c r="P14" s="6"/>
       <c r="Q14" s="11"/>
     </row>
-    <row r="15" spans="1:17" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" s="23" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="18">
         <v>12</v>
       </c>
@@ -1392,7 +1399,7 @@
       <c r="P15" s="20"/>
       <c r="Q15" s="22"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="5">
         <v>13</v>
       </c>
@@ -1402,7 +1409,9 @@
       <c r="C16" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="6"/>
+      <c r="D16" s="6">
+        <v>2019</v>
+      </c>
       <c r="E16" s="6">
         <v>0</v>
       </c>
@@ -1420,12 +1429,14 @@
       <c r="K16" s="6"/>
       <c r="L16" s="8"/>
       <c r="M16" s="6"/>
-      <c r="N16" s="6"/>
+      <c r="N16" s="6" t="s">
+        <v>121</v>
+      </c>
       <c r="O16" s="6"/>
       <c r="P16" s="6"/>
       <c r="Q16" s="11"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="5">
         <v>14</v>
       </c>
@@ -1462,7 +1473,7 @@
       <c r="P17" s="6"/>
       <c r="Q17" s="11"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="5">
         <v>15</v>
       </c>
@@ -1499,7 +1510,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="5">
         <v>16</v>
       </c>
@@ -1534,7 +1545,7 @@
       <c r="P19" s="6"/>
       <c r="Q19" s="11"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="5">
         <v>17</v>
       </c>
@@ -1569,7 +1580,7 @@
       <c r="P20" s="6"/>
       <c r="Q20" s="11"/>
     </row>
-    <row r="21" spans="1:17" s="23" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" s="23" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="18">
         <v>18</v>
       </c>
@@ -1606,7 +1617,7 @@
       <c r="P21" s="20"/>
       <c r="Q21" s="22"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="5">
         <v>19</v>
       </c>
@@ -1641,7 +1652,7 @@
       <c r="P22" s="6"/>
       <c r="Q22" s="11"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="5">
         <v>20</v>
       </c>
@@ -1676,7 +1687,7 @@
       <c r="P23" s="6"/>
       <c r="Q23" s="11"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="5">
         <v>21</v>
       </c>
@@ -1686,7 +1697,9 @@
       <c r="C24" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D24" s="6"/>
+      <c r="D24" s="6">
+        <v>2024</v>
+      </c>
       <c r="E24" s="6">
         <v>0</v>
       </c>
@@ -1709,7 +1722,7 @@
       <c r="P24" s="6"/>
       <c r="Q24" s="11"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="5">
         <v>22</v>
       </c>
@@ -1719,7 +1732,9 @@
       <c r="C25" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="D25" s="6"/>
+      <c r="D25" s="6">
+        <v>2024</v>
+      </c>
       <c r="E25" s="6">
         <v>1</v>
       </c>
@@ -1742,7 +1757,7 @@
       <c r="P25" s="6"/>
       <c r="Q25" s="11"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="5">
         <v>23</v>
       </c>
@@ -1777,7 +1792,7 @@
       <c r="P26" s="6"/>
       <c r="Q26" s="11"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="5">
         <v>24</v>
       </c>
@@ -1812,7 +1827,7 @@
       <c r="P27" s="6"/>
       <c r="Q27" s="11"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="5">
         <v>25</v>
       </c>
@@ -1847,7 +1862,7 @@
       <c r="P28" s="6"/>
       <c r="Q28" s="11"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="5">
         <v>26</v>
       </c>
@@ -1882,22 +1897,22 @@
       <c r="P29" s="6"/>
       <c r="Q29" s="11"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="17" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="23" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" t="s">
         <v>102</v>
       </c>

--- a/literature-review/initial-search/initial_search_topic2.xlsx
+++ b/literature-review/initial-search/initial_search_topic2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\177020724\Documents\Studium\Thesis\Literature Review\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F7DA24F-C4FB-4615-BA28-177150A46D4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1C7255E-35E5-4204-A515-F1FA28471A1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4488" yWindow="936" windowWidth="30960" windowHeight="14244" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20544" yWindow="-3036" windowWidth="23232" windowHeight="12432" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -867,16 +867,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="31.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="31.1015625" defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="5.77734375" customWidth="1"/>
-    <col min="2" max="2" width="60.77734375" customWidth="1"/>
-    <col min="3" max="3" width="30.77734375" customWidth="1"/>
-    <col min="4" max="8" width="10.77734375" customWidth="1"/>
-    <col min="9" max="16" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="5.7890625" customWidth="1"/>
+    <col min="2" max="2" width="60.7890625" customWidth="1"/>
+    <col min="3" max="3" width="30.7890625" customWidth="1"/>
+    <col min="4" max="8" width="10.7890625" customWidth="1"/>
+    <col min="9" max="16" width="8.7890625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="I1" s="2" t="s">
         <v>111</v>
       </c>
@@ -887,7 +887,7 @@
       </c>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="3" t="s">
         <v>103</v>
       </c>
@@ -940,7 +940,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="5">
         <v>0</v>
       </c>
@@ -977,7 +977,7 @@
       <c r="P3" s="6"/>
       <c r="Q3" s="11"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="5">
         <v>1</v>
       </c>
@@ -1012,7 +1012,7 @@
       <c r="P4" s="6"/>
       <c r="Q4" s="11"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="5">
         <v>2</v>
       </c>
@@ -1047,7 +1047,7 @@
       <c r="P5" s="6"/>
       <c r="Q5" s="11"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="5">
         <v>3</v>
       </c>
@@ -1082,7 +1082,7 @@
       <c r="P6" s="6"/>
       <c r="Q6" s="11"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="5">
         <v>4</v>
       </c>
@@ -1123,7 +1123,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="5">
         <v>5</v>
       </c>
@@ -1158,7 +1158,7 @@
       <c r="P8" s="6"/>
       <c r="Q8" s="11"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="5">
         <v>6</v>
       </c>
@@ -1193,7 +1193,7 @@
       <c r="P9" s="6"/>
       <c r="Q9" s="11"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="5">
         <v>7</v>
       </c>
@@ -1228,7 +1228,7 @@
       <c r="P10" s="6"/>
       <c r="Q10" s="11"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="5">
         <v>8</v>
       </c>
@@ -1263,7 +1263,7 @@
       <c r="P11" s="6"/>
       <c r="Q11" s="11"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="5">
         <v>9</v>
       </c>
@@ -1300,7 +1300,7 @@
       <c r="P12" s="6"/>
       <c r="Q12" s="11"/>
     </row>
-    <row r="13" spans="1:17" s="24" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:17" s="24" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="19">
         <v>10</v>
       </c>
@@ -1337,7 +1337,7 @@
       <c r="P13" s="21"/>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="5">
         <v>11</v>
       </c>
@@ -1372,7 +1372,7 @@
       <c r="P14" s="6"/>
       <c r="Q14" s="11"/>
     </row>
-    <row r="15" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="13">
         <v>12</v>
       </c>
@@ -1409,7 +1409,7 @@
       <c r="P15" s="15"/>
       <c r="Q15" s="17"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="5">
         <v>13</v>
       </c>
@@ -1446,7 +1446,7 @@
       <c r="P16" s="6"/>
       <c r="Q16" s="11"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="5">
         <v>14</v>
       </c>
@@ -1483,7 +1483,7 @@
       <c r="P17" s="6"/>
       <c r="Q17" s="11"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="5">
         <v>15</v>
       </c>
@@ -1520,7 +1520,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="5">
         <v>16</v>
       </c>
@@ -1555,7 +1555,7 @@
       <c r="P19" s="6"/>
       <c r="Q19" s="11"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="5">
         <v>17</v>
       </c>
@@ -1590,7 +1590,7 @@
       <c r="P20" s="6"/>
       <c r="Q20" s="11"/>
     </row>
-    <row r="21" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:17" s="18" customFormat="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="13">
         <v>18</v>
       </c>
@@ -1627,7 +1627,7 @@
       <c r="P21" s="15"/>
       <c r="Q21" s="17"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="5">
         <v>19</v>
       </c>
@@ -1662,7 +1662,7 @@
       <c r="P22" s="6"/>
       <c r="Q22" s="11"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="5">
         <v>20</v>
       </c>
@@ -1697,7 +1697,7 @@
       <c r="P23" s="6"/>
       <c r="Q23" s="11"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="5">
         <v>21</v>
       </c>
@@ -1732,7 +1732,7 @@
       <c r="P24" s="6"/>
       <c r="Q24" s="11"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="5">
         <v>22</v>
       </c>
@@ -1767,7 +1767,7 @@
       <c r="P25" s="6"/>
       <c r="Q25" s="11"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="5">
         <v>23</v>
       </c>
@@ -1802,7 +1802,7 @@
       <c r="P26" s="6"/>
       <c r="Q26" s="11"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="5">
         <v>24</v>
       </c>
@@ -1837,7 +1837,7 @@
       <c r="P27" s="6"/>
       <c r="Q27" s="11"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="5">
         <v>25</v>
       </c>
@@ -1872,7 +1872,7 @@
       <c r="P28" s="6"/>
       <c r="Q28" s="11"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="5">
         <v>26</v>
       </c>
@@ -1907,22 +1907,22 @@
       <c r="P29" s="6"/>
       <c r="Q29" s="11"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B31" s="12" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.55000000000000004">
       <c r="B32" s="18" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B34" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B35" t="s">
         <v>102</v>
       </c>
